--- a/previews/pr-145/working/fhir/ps/1.0.0-ci-build/StructureDefinition-au-ps-smokingstatus.xlsx
+++ b/previews/pr-145/working/fhir/ps/1.0.0-ci-build/StructureDefinition-au-ps-smokingstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T03:09:13+00:00</t>
+    <t>2026-06-19T08:07:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
